--- a/Tagihan/2026/Juli/H. Surian 2.xlsx
+++ b/Tagihan/2026/Juli/H. Surian 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data-Pekerjaan\Tagihan\2026\Juli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4840EDC1-ECA3-468C-AE4E-70D836F2AD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A55F6F-951A-4B2B-A9DC-1751120561CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="720" windowWidth="19410" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>NO.</t>
   </si>
@@ -166,6 +166,12 @@
     <t>Biaya Perbaikan</t>
   </si>
   <si>
+    <t>Service AC</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
     <r>
       <t>Tanjung,</t>
     </r>
@@ -177,14 +183,20 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> 05 Juli 2026</t>
+      <t xml:space="preserve"> 27 Juli 2026</t>
     </r>
   </si>
   <si>
-    <t>Service AC</t>
-  </si>
-  <si>
-    <t>Unit</t>
+    <t>Camera Hikvision ColorVU Audio</t>
+  </si>
+  <si>
+    <t>Camera Hikvision SmartCOlor 2way Audio</t>
+  </si>
+  <si>
+    <t>Kabel CCTV Outdoor</t>
+  </si>
+  <si>
+    <t>Setting Dan Instalasi</t>
   </si>
 </sst>
 </file>
@@ -192,7 +204,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -626,38 +638,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -708,7 +720,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -729,11 +741,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -829,13 +841,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1224,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:H41"/>
+  <dimension ref="B5:H47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1291,7 +1303,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G13" s="52"/>
     </row>
@@ -1518,7 +1530,7 @@
         <v>150000</v>
       </c>
       <c r="G28" s="25">
-        <f t="shared" ref="G28:G30" si="2">F28*D28</f>
+        <f t="shared" ref="G28:G36" si="2">F28*D28</f>
         <v>150000</v>
       </c>
     </row>
@@ -1548,13 +1560,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="2">
         <v>2</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" s="23">
         <v>100000</v>
@@ -1565,88 +1577,214 @@
       </c>
     </row>
     <row r="31" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="24"/>
-    </row>
-    <row r="32" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="47" t="s">
+      <c r="B31" s="2">
         <v>4</v>
       </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="27">
-        <f>SUM(G17:G31)</f>
-        <v>1260000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
-    </row>
-    <row r="35" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B35" s="50" t="s">
+      <c r="C31" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="23">
+        <v>450000</v>
+      </c>
+      <c r="G31" s="25">
+        <f t="shared" si="2"/>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="51" t="s">
+      <c r="C32" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="23">
+        <v>550000</v>
+      </c>
+      <c r="G32" s="25">
+        <f t="shared" si="2"/>
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2">
         <v>6</v>
       </c>
-      <c r="G35" s="51"/>
-    </row>
-    <row r="39" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="45" t="s">
+      <c r="C33" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="2">
+        <v>85</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G33" s="25">
+        <f t="shared" si="2"/>
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>7</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="23">
+        <v>15000</v>
+      </c>
+      <c r="G34" s="25">
+        <f t="shared" si="2"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="2">
+        <v>8</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="23">
+        <v>15000</v>
+      </c>
+      <c r="G35" s="25">
+        <f t="shared" si="2"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>9</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="23">
+        <v>150000</v>
+      </c>
+      <c r="G36" s="25">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" spans="2:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="27">
+        <f>SUM(G17:G37)</f>
+        <v>3045000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17"/>
+    </row>
+    <row r="41" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B41" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="50"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="51"/>
+    </row>
+    <row r="45" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="21"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="42" t="s">
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="21"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B47:G47"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="F41:G41"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
